--- a/examples/sample_bank.xlsx
+++ b/examples/sample_bank.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,6 +889,58 @@
         </is>
       </c>
       <c r="L9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Geetanjali prepares a drip-irrigation solution where fertilizer concentrate and water are mixed in the ratio &lt;strong&gt;3 : 22&lt;/strong&gt;. The total solution required for one field section is &lt;strong&gt;475 litres&lt;/strong&gt;. How many litres of fertilizer concentrate are needed?&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;57 litres&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;60 litres&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;63.5 litres&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;71.25 litres&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>option1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MULTIPLE_CHOICE_QUESTION</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Quantitative Ability</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Ratios and Proportions</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
